--- a/resources/HOD & N+1.xlsx
+++ b/resources/HOD & N+1.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NVL-04.06.2020\Imformation Management\Moloy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\vms\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E967233-CF40-418E-8FA4-FBD74A506998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D21E438-3296-486B-82BC-C1CECEBC93B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{C03F7CDF-22E0-4303-A95A-545AF0D8EBD4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C03F7CDF-22E0-4303-A95A-545AF0D8EBD4}"/>
   </bookViews>
   <sheets>
     <sheet name="HOD" sheetId="3" r:id="rId1"/>
     <sheet name="N+1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HOD!$B$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HOD!$B$1:$H$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'N+1'!$B$1:$I$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -546,16 +546,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -564,21 +564,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -982,28 +981,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7168F1-0613-4E48-9A98-9EE814C8AB42}">
   <dimension ref="B1:H17"/>
-  <sheetFormatPr defaultColWidth="9.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1016,20 +1015,20 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B2" s="8">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <v>30004460</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -1039,21 +1038,21 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B3" s="8">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="7">
         <f>B2+1</f>
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="C3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>30008419</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -1063,21 +1062,21 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B4" s="8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="7">
         <f t="shared" ref="B4:B17" si="0">B3+1</f>
         <v>3</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>30008612</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -1087,21 +1086,21 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" s="8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>30010957</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -1111,21 +1110,21 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B6" s="8">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="12" t="s">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>30002410</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1135,21 +1134,21 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B7" s="8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>30011507</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1159,21 +1158,21 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8" s="8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="C8" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>30008656</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1183,21 +1182,21 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B9" s="8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>30008656</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1207,21 +1206,21 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B10" s="8">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="7">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="C10" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>30010514</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -1231,21 +1230,21 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B11" s="8">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="7">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="12" t="s">
+      <c r="C11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>30008525</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -1255,21 +1254,21 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B12" s="8">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="7">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C12" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>30008571</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1279,21 +1278,21 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B13" s="8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="7">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>30008401</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -1303,21 +1302,21 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B14" s="8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="7">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>30008500</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1327,21 +1326,21 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="8">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="7">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="12" t="s">
+      <c r="C15" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>30009017</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -1351,21 +1350,21 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="7">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="C16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>30006677</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -1375,21 +1374,21 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B17" s="8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="7">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="C17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>30008786</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -1400,15 +1399,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:H1" xr:uid="{CD7168F1-0613-4E48-9A98-9EE814C8AB42}"/>
-  <conditionalFormatting sqref="G1">
-    <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
-      <formula>AND(COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)&gt;1,NOT(ISBLANK(G1)))</formula>
+  <autoFilter ref="B1:H17" xr:uid="{CD7168F1-0613-4E48-9A98-9EE814C8AB42}"/>
+  <conditionalFormatting sqref="F1:F17">
+    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+      <formula>AND(COUNTIF($B$1:$B$32, F1)+COUNTIF($B$33:$B$65358, F1)&gt;1,NOT(ISBLANK(F1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F17">
-    <cfRule type="expression" dxfId="4" priority="3" stopIfTrue="1">
-      <formula>AND(COUNTIF($B$1:$B$32, F1)+COUNTIF($B$33:$B$65358, F1)&gt;1,NOT(ISBLANK(F1)))</formula>
+  <conditionalFormatting sqref="G1">
+    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
+      <formula>AND(COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)&gt;1,NOT(ISBLANK(G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G17">
@@ -1423,23 +1422,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC9E2398-9C37-4387-BD38-014652A57577}">
   <dimension ref="B1:H42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.36328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1455,8 +1454,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B2" s="8">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
@@ -1478,8 +1477,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B3" s="8">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="7">
         <f t="shared" ref="B3:B42" si="0">B2+1</f>
         <v>2</v>
       </c>
@@ -1502,8 +1501,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B4" s="8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1526,8 +1525,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" s="8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1550,8 +1549,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B6" s="8">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1574,8 +1573,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B7" s="8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1598,8 +1597,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8" s="8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1622,8 +1621,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B9" s="8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1646,8 +1645,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B10" s="8">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="7">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1670,8 +1669,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B11" s="8">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="7">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1694,8 +1693,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B12" s="8">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="7">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1718,8 +1717,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B13" s="8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="7">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1742,8 +1741,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B14" s="8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="7">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1766,8 +1765,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="8">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="7">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1790,8 +1789,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="7">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1814,8 +1813,8 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B17" s="8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="7">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1838,8 +1837,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="7">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1862,8 +1861,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B19" s="8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="7">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1886,8 +1885,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B20" s="8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="7">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1910,8 +1909,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="7">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1934,8 +1933,8 @@
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B22" s="8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="7">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -1958,8 +1957,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B23" s="8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="7">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -1982,8 +1981,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B24" s="8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="7">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -2006,8 +2005,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B25" s="8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="7">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -2030,8 +2029,8 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B26" s="8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="7">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -2054,8 +2053,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B27" s="8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="7">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -2078,8 +2077,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B28" s="8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="7">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -2102,8 +2101,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B29" s="8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="7">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -2126,8 +2125,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B30" s="8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="7">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -2150,8 +2149,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B31" s="8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="7">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -2174,8 +2173,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B32" s="8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="7">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -2198,8 +2197,8 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B33" s="8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="7">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -2222,8 +2221,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B34" s="8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="7">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -2246,8 +2245,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B35" s="8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="7">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -2270,8 +2269,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B36" s="8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="7">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -2294,8 +2293,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B37" s="8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="7">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -2318,8 +2317,8 @@
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B38" s="8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="7">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -2342,8 +2341,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B39" s="8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="7">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -2366,8 +2365,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B40" s="8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="7">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -2390,8 +2389,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B41" s="8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="7">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -2414,8 +2413,8 @@
         <v>130</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B42" s="8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="7">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -2440,19 +2439,19 @@
     </row>
   </sheetData>
   <autoFilter ref="B1:I42" xr:uid="{EC9E2398-9C37-4387-BD38-014652A57577}"/>
+  <conditionalFormatting sqref="F1:F42">
+    <cfRule type="expression" dxfId="2" priority="242" stopIfTrue="1">
+      <formula>AND(COUNTIF($B$1:$B$32, F1)+COUNTIF($B$33:$B$65358, F1)&gt;1,NOT(ISBLANK(F1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G1">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>AND(COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)+COUNTIF(#REF!, G1)&gt;1,NOT(ISBLANK(G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G42">
-    <cfRule type="expression" dxfId="1" priority="241" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="241" stopIfTrue="1">
       <formula>AND(COUNTIF($I$3:$I$32, G2)+COUNTIF($I$31:$I$34, G2)&gt;1,NOT(ISBLANK(G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F42">
-    <cfRule type="expression" dxfId="0" priority="242" stopIfTrue="1">
-      <formula>AND(COUNTIF($B$1:$B$32, F1)+COUNTIF($B$33:$B$65358, F1)&gt;1,NOT(ISBLANK(F1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -2466,6 +2465,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0" xsi:nil="true"/>
+    <MigrationWizIdPermissions xmlns="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0" xsi:nil="true"/>
+    <MigrationWizId xmlns="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006EF922C2DD7A374FA560F22F8D1259FE" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b8cd667aff2f9a92aaa8f17322f38616">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0" xmlns:ns4="dd7bb5cb-5cf8-4de9-bf7d-51b97c76b0d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e340f0b92ddb0f4a788b7b76cf6a11b5" ns3:_="" ns4:_="">
     <xsd:import namespace="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0"/>
@@ -2722,27 +2741,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF6A9443-32E6-46EA-BE41-E3AF98F937E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="dd7bb5cb-5cf8-4de9-bf7d-51b97c76b0d5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0" xsi:nil="true"/>
-    <MigrationWizIdPermissions xmlns="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0" xsi:nil="true"/>
-    <MigrationWizId xmlns="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F49EDAA-5189-4456-96FB-BB216E50D618}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CE99F91-524B-4960-8AA9-89E17792E2C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2759,29 +2783,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F49EDAA-5189-4456-96FB-BB216E50D618}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF6A9443-32E6-46EA-BE41-E3AF98F937E8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5d78f9de-f46b-4407-bb7c-faf0f3cb7fd0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="dd7bb5cb-5cf8-4de9-bf7d-51b97c76b0d5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>